--- a/exports/34721_lurinchincha.xlsx
+++ b/exports/34721_lurinchincha.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1431,45 +1431,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>76293885</t>
+          <t>94738019</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>ASTO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>GOSME</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOSELYN MARDHELY</t>
+          <t>FREY ERLING DARIEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14/02/2006</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,40 +1494,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>43158719</t>
+          <t>76293885</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NICOLAIN</t>
+          <t>JOSELYN MARDHELY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14/08/1985</t>
+          <t>14/02/2006</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1557,40 +1557,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>75626359</t>
+          <t>43158719</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AURIS</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BILLAVERDE</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CARLA VALERIA</t>
+          <t>NICOLAIN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/09/2000</t>
+          <t>14/08/1985</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,45 +1620,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>94343751</t>
+          <t>75626359</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>AURIS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MALLASCA</t>
+          <t>BILLAVERDE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LIAM GAEL</t>
+          <t>CARLA VALERIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>18/09/2000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13/08/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,22 +1683,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>91966118</t>
+          <t>94343751</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>MALLASCA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LUIS CHARLES</t>
+          <t>LIAM GAEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>09/08/2020</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>13/08/2025</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,22 +1746,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>71205808</t>
+          <t>91966118</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MUENA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>LUIS CHARLES</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1770,16 +1770,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01/05/1996</t>
+          <t>09/08/2020</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1935,22 +1935,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>94678867</t>
+          <t>92507704</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>BRAMA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>YASURI ROSITA</t>
+          <t>DELSY ROSMERI</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1959,11 +1959,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/08/2021</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>74282565</t>
+          <t>94678867</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2008,35 +2008,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OROSCO</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>YASURI ROSITA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/10/1999</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,22 +2061,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>46048783</t>
+          <t>74282565</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CACHIQUE</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MERMAO</t>
+          <t>OROSCO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DANY BLAIR</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21/10/1989</t>
+          <t>04/10/1999</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,45 +2124,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>81912306</t>
+          <t>46048783</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CAHUIN</t>
+          <t>CACHIQUE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MERMAO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AINHOA ALISSANDRA</t>
+          <t>DANY BLAIR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>21/10/1989</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,45 +2187,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20027289</t>
+          <t>81912306</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CAHUIN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>AINHOA ALISSANDRA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15/01/1968</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>92149750</t>
+          <t>20027289</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2260,35 +2260,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JENNIFER ANDREA</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>15/01/1968</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,27 +2313,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>91992750</t>
+          <t>92149750</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CALLE</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JACOB</t>
+          <t>JENNIFER ANDREA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,35 +2376,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>92444536</t>
+          <t>91992750</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CALLE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MUNIVE</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VELIANKA</t>
+          <t>JACOB</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,35 +2439,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>91897651</t>
+          <t>92444536</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASIMIRO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>MUNIVE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ELVIN YEIKO</t>
+          <t>VELIANKA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,45 +2502,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>94539160</t>
+          <t>74977236</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CANCHARI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BRIANA AMELIA</t>
+          <t>ANIBAL JULHIÑO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>17/03/2002</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>11/06/2013</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>72897620</t>
+          <t>91897651</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>CASIMIRO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>ELVIN YEIKO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>07/11/1996</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,22 +2628,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>60948581</t>
+          <t>94539160</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>STEPHANIE MISHELLE</t>
+          <t>BRIANA AMELIA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19/04/2001</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,22 +2691,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>41891670</t>
+          <t>72897620</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WALTER HUGO</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>08/06/1982</t>
+          <t>07/11/1996</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>94670548</t>
+          <t>60948581</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,35 +2764,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>STEPHANIE MISHELLE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>19/04/2001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,22 +2817,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>94295173</t>
+          <t>41891670</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CATEÑO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JHON WILLIAMS</t>
+          <t>WALTER HUGO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>02/08/2017</t>
+          <t>08/06/1982</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,35 +2880,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>94356549</t>
+          <t>94670548</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ZEINEP ABIGAIL</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22/08/2025</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,22 +2943,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>93985686</t>
+          <t>94295173</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CCOICCA</t>
+          <t>CATEÑO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EVANGELISTA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GAEL ALEXANDER</t>
+          <t>JHON WILLIAMS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23/09/2024</t>
+          <t>02/08/2017</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,22 +3006,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>81912333</t>
+          <t>94356549</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CCORAHUA</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MAYHUA</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BELEN YAMILETH</t>
+          <t>ZEINEP ABIGAIL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3030,11 +3030,11 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>22/08/2025</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,22 +3069,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>94220420</t>
+          <t>93985686</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CELSO</t>
+          <t>CCOICCA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>EVANGELISTA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ETHAN ALDO</t>
+          <t>GAEL ALEXANDER</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22/04/2025</t>
+          <t>23/09/2024</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,22 +3132,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>91883722</t>
+          <t>81912333</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>CCORAHUA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>MAYHUA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAYNETH JHOANNA</t>
+          <t>BELEN YAMILETH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3156,11 +3156,11 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,22 +3195,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>91898061</t>
+          <t>94220420</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CHAVARRIAS</t>
+          <t>CELSO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ZENDER LIAN</t>
+          <t>ETHAN ALDO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3219,11 +3219,11 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>22/04/2025</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,35 +3258,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>94241992</t>
+          <t>91883722</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DE LA FUENTE</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ANGELO EZEQUIEL</t>
+          <t>SAYNETH JHOANNA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>91754386</t>
+          <t>91898061</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>CHAVARRIAS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DEID ALEXANDER</t>
+          <t>ZENDER LIAN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,35 +3384,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>92321088</t>
+          <t>94241992</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CHUMPATI</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>DE LA FUENTE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ROSA</t>
+          <t>ANGELO EZEQUIEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/04/2021</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,40 +3447,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>44503468</t>
+          <t>92456436</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CHUMPE</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>ANDREA ROCIO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>08/02/1983</t>
+          <t>20/07/2021</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,45 +3510,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>77503900</t>
+          <t>91754386</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COLACHAGUA</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SHEILA LETICIA</t>
+          <t>DEID ALEXANDER</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>08/10/1995</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>92039400</t>
+          <t>92321088</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CHUMPATI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAÑARI</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AZUMI SHANTAL</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>29/09/2020</t>
+          <t>18/04/2021</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,40 +3636,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>71718570</t>
+          <t>44503468</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CHUMPE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GALA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PATSI CINTHIA</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>05/02/2001</t>
+          <t>08/02/1983</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,35 +3699,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>46791163</t>
+          <t>77503900</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COTERA</t>
+          <t>COLACHAGUA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RODIL RENE</t>
+          <t>SHEILA LETICIA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16/12/1990</t>
+          <t>08/10/1995</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,22 +3762,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00092715</t>
+          <t>92039400</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CUEVA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RICOPA</t>
+          <t>CAÑARI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ROSA MERY</t>
+          <t>AZUMI SHANTAL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>07/06/1971</t>
+          <t>29/09/2020</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,45 +3825,45 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>92446495</t>
+          <t>71718570</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DAHUA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RUPAY</t>
+          <t>GALA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DEYVI JACK</t>
+          <t>PATSI CINTHIA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13/07/2021</t>
+          <t>05/02/2001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,45 +3888,45 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>94396233</t>
+          <t>75287007</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DEXTRE</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>ENERO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>GAEL KAYRO</t>
+          <t>KETTY DOMINICA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>30/09/1999</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>92207811</t>
+          <t>46791163</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>COTERA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ERIK</t>
+          <t>RODIL RENE</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>16/12/1990</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,45 +4014,45 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>92222315</t>
+          <t>00092715</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>CUEVA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>RICOPA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ABDIEL JAZIEL</t>
+          <t>ROSA MERY</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>07/06/1971</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,45 +4077,45 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>42413512</t>
+          <t>92446495</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>DAHUA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RUPAY</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JAZMIN BETZABETH</t>
+          <t>DEYVI JACK</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11/05/1984</t>
+          <t>13/07/2021</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,35 +4140,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>92489713</t>
+          <t>94396233</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>DEXTRE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>INGRID ASTRID</t>
+          <t>GAEL KAYRO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,40 +4203,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>75318534</t>
+          <t>92207811</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ARISBEL ARIANA</t>
+          <t>ERIK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>09/04/2006</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>76156896</t>
+          <t>92222315</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EUSTAQUIO</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BENITES</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JAVIER</t>
+          <t>ABDIEL JAZIEL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>09/07/1999</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4329,22 +4329,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>92194218</t>
+          <t>42413512</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ESPINO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>JAZMIN BETZABETH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,21 +4353,21 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>11/05/1984</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,27 +4392,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>92222175</t>
+          <t>92489713</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>GARCIA</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>PORTOCARRERO</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SAMIR MILER</t>
+          <t>INGRID ASTRID</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,40 +4455,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>42214488</t>
+          <t>75318534</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JAIME TEOFILO</t>
+          <t>ARISBEL ARIANA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>12/08/1982</t>
+          <t>09/04/2006</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,45 +4518,45 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>94642996</t>
+          <t>76156896</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GASTELU</t>
+          <t>EUSTAQUIO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CABEZAS</t>
+          <t>BENITES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ABIGAIL MEDALI</t>
+          <t>JAVIER</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>09/07/1999</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,35 +4581,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>94445786</t>
+          <t>92194218</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>ESPINO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CLEIDER</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,22 +4644,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>91885374</t>
+          <t>92222175</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GUEROVICH</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ARANCEL</t>
+          <t>PORTOCARRERO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ADRIEL JORGE</t>
+          <t>SAMIR MILER</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,11 +4668,11 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>09/06/2020</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,22 +4707,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>75101251</t>
+          <t>42214488</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GUILLEN</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ELMER</t>
+          <t>JAIME TEOFILO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14/01/2001</t>
+          <t>12/08/1982</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,22 +4770,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20996386</t>
+          <t>94642996</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUAMANCHAHUA</t>
+          <t>GASTELU</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CABEZAS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FRICIA ELIZABETH</t>
+          <t>ABIGAIL MEDALI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4794,21 +4794,21 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02/06/1971</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,35 +4833,35 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>94047252</t>
+          <t>94445786</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HUANICO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>CLEIDER</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,45 +4896,45 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>78765946</t>
+          <t>91885374</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>GUEROVICH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ARANCEL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>YARISLEY DAFNE</t>
+          <t>ADRIEL JORGE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>24/08/2014</t>
+          <t>09/06/2020</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,27 +4959,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>70809810</t>
+          <t>75101251</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>GUILLEN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JAQUELINE MAYUMI</t>
+          <t>ELMER</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>15/08/2001</t>
+          <t>14/01/2001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>92445032</t>
+          <t>76918087</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>GUIZADO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LINDA YEIS</t>
+          <t>RANDY</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>05/02/1998</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,35 +5085,35 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>42901772</t>
+          <t>20996386</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>HUAMANCHAHUA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>FRICIA ELIZABETH</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>06/08/1982</t>
+          <t>02/06/1971</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,35 +5148,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>92082689</t>
+          <t>94047252</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LANAZCA</t>
+          <t>HUANICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SIERRA</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>JORGE ALEJANDRO</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>28/10/2020</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5211,40 +5211,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>75001764</t>
+          <t>78765946</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LUIGUI DANIEL</t>
+          <t>YARISLEY DAFNE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>13/04/2001</t>
+          <t>24/08/2014</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,35 +5274,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>76412062</t>
+          <t>70809810</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SERGIO RAFAEL</t>
+          <t>JAQUELINE MAYUMI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14/11/2003</t>
+          <t>15/08/2001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,27 +5337,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>92193263</t>
+          <t>92445032</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LIMACHE</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>IKER NOAH</t>
+          <t>LINDA YEIS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20580064</t>
+          <t>42901772</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LLANCACHAGUA</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HUACCHO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JORGE PAPA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,16 +5424,16 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23/06/1944</t>
+          <t>06/08/1982</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,35 +5463,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>92469548</t>
+          <t>92082689</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LOZADA</t>
+          <t>LANAZCA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>SIERRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CATALEYA ZEYNEP</t>
+          <t>JORGE ALEJANDRO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>28/10/2020</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,40 +5526,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>43511339</t>
+          <t>75001764</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ECHABAUDES</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DAYSY</t>
+          <t>LUIGUI DANIEL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>19/12/1985</t>
+          <t>13/04/2001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,45 +5589,45 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>94615934</t>
+          <t>76412062</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MALVEÑO</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MAYURI</t>
+          <t>SERGIO RAFAEL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>14/11/2003</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>70606096</t>
+          <t>92193263</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>LIMACHE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PERCY JESUS</t>
+          <t>IKER NOAH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>05/08/1998</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>94618669</t>
+          <t>20580064</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MATA</t>
+          <t>LLANCACHAGUA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>HUACCHO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EMIR RUBEN</t>
+          <t>JORGE PAPA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>23/06/1944</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,35 +5778,35 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>92039861</t>
+          <t>92469548</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MATENCIOS</t>
+          <t>LOZADA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>JHASTIN YANDEL</t>
+          <t>CATALEYA ZEYNEP</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>30/09/2020</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>94307754</t>
+          <t>43511339</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MAYBANTI</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ÑACO</t>
+          <t>ECHABAUDES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MEDALY ESTHER</t>
+          <t>DAYSY</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>19/12/1985</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,22 +5904,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>92194352</t>
+          <t>94615934</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MALVEÑO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PILAR INGRID</t>
+          <t>MAYURI</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5928,11 +5928,11 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,22 +5967,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>77016635</t>
+          <t>70606096</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BERRY</t>
+          <t>PERCY JESUS</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5991,11 +5991,11 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>19/11/2001</t>
+          <t>05/08/1998</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,22 +6030,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>76321000</t>
+          <t>94618669</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MELGAREJO</t>
+          <t>MATA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE</t>
+          <t>EMIR RUBEN</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6054,21 +6054,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14/12/2001</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,22 +6093,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>47211525</t>
+          <t>92039861</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MATENCIOS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BELLIDO</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MARCIAL LINDO</t>
+          <t>JHASTIN YANDEL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,21 +6117,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>03/03/1991</t>
+          <t>30/09/2020</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>77042300</t>
+          <t>94307754</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MAYBANTI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>ÑACO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>JENNIFER PILAR</t>
+          <t>MEDALY ESTHER</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>01/08/2005</t>
+          <t>09/07/2025</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>77418210</t>
+          <t>92194352</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MERINO</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ENCISO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>JUDITH</t>
+          <t>PILAR INGRID</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,21 +6243,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>28/02/1999</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,45 +6282,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>92040429</t>
+          <t>77016635</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>BERRY</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>30/09/2020</t>
+          <t>19/11/2001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,22 +6345,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>41594775</t>
+          <t>76321000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MELGAREJO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>HERNAN</t>
+          <t>LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6369,16 +6369,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>25/10/1982</t>
+          <t>14/12/2001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,45 +6408,45 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>92192495</t>
+          <t>47211525</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>BELLIDO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ALESSIA YATZIRI</t>
+          <t>MARCIAL LINDO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>03/03/1991</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,22 +6471,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>47760020</t>
+          <t>74281497</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MUNGUI</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ZACARIAS</t>
+          <t>ATAPOMA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CLEVER</t>
+          <t>ELDER MESIAS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,11 +6495,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>19/10/1989</t>
+          <t>12/07/1995</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>92911456</t>
+          <t>77042300</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MURAYARI</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LOZANO</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>YARITZA ITZEL</t>
+          <t>JENNIFER PILAR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>29/05/2022</t>
+          <t>01/08/2005</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,35 +6597,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>76927877</t>
+          <t>77418210</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MERINO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ENCISO</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>JUAN DAVID</t>
+          <t>JUDITH</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>06/04/2006</t>
+          <t>28/02/1999</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,35 +6660,35 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>94682414</t>
+          <t>92040429</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RONY CESAR</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>30/09/2020</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>94398586</t>
+          <t>41594775</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ZACARIAS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ZHENYI KENYI</t>
+          <t>HERNAN</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>28/09/2025</t>
+          <t>25/10/1982</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>91883930</t>
+          <t>92192495</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HUAYA</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ARIANA AMELY</t>
+          <t>ALESSIA YATZIRI</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,35 +6849,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>46449555</t>
+          <t>47760020</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>MUNGUI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BRAÑES</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NADIA TANIA</t>
+          <t>CLEVER</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>28/04/1990</t>
+          <t>19/10/1989</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>41517689</t>
+          <t>92911456</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MURAYARI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>LOZANO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NILDA YANET</t>
+          <t>YARITZA ITZEL</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>15/10/1982</t>
+          <t>29/05/2022</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>92489139</t>
+          <t>76927877</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OSORES</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LLAMUCO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>IAN KARPER</t>
+          <t>JUAN DAVID</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>06/04/2006</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,22 +7038,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>92087755</t>
+          <t>94682414</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ALFONSO BRANT</t>
+          <t>RONY CESAR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>31/10/2020</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>91885525</t>
+          <t>94398586</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PACHIRI</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CAYETANO</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>JUAN BENJAMIN</t>
+          <t>ZHENYI KENYI</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,11 +7125,11 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>09/06/2020</t>
+          <t>28/09/2025</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,35 +7164,35 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>94191376</t>
+          <t>91883930</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PAIMA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>QUENTISHA</t>
+          <t>HUAYA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LIAM MAIKEL</t>
+          <t>ARIANA AMELY</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,45 +7227,45 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>92451937</t>
+          <t>46449555</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>HUARACC</t>
+          <t>BRAÑES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NEHEMIAS RICHARD</t>
+          <t>NADIA TANIA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>28/04/1990</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,22 +7290,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>82244708</t>
+          <t>41517689</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PATRICIO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SANTOMA</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>NILDA YANET</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>15/10/1982</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,45 +7353,45 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>49103748</t>
+          <t>92489139</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PICHUCA</t>
+          <t>OSORES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PIUNCA</t>
+          <t>LLAMUCO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>HILARIA</t>
+          <t>IAN KARPER</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>30/03/1956</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,35 +7416,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>92222558</t>
+          <t>92087755</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PIORI</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SHUNAXHI SUSEJ</t>
+          <t>ALFONSO BRANT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>31/10/2020</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,45 +7479,45 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>80581038</t>
+          <t>91885525</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PIZANGO</t>
+          <t>PACHIRI</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>CAYETANO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ARMILDA</t>
+          <t>JUAN BENJAMIN</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>23/11/1977</t>
+          <t>09/06/2020</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,22 +7542,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>41898437</t>
+          <t>94191376</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PLAZA</t>
+          <t>PAIMA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>QUENTISHA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MELVIN ANGEL</t>
+          <t>LIAM MAIKEL</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>27/01/1983</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>75313928</t>
+          <t>92451937</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>HUARACC</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DAMMARO LUCERO</t>
+          <t>NEHEMIAS RICHARD</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>19/07/2005</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,35 +7668,35 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>91689899</t>
+          <t>82244708</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PUENTE</t>
+          <t>PATRICIO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>SANTOMA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EDRICK LEODAD JHONNY</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,45 +7731,45 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>92464778</t>
+          <t>49103748</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>PICHUCA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CHIMANCA</t>
+          <t>PIUNCA</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ELFREN HONLY</t>
+          <t>HILARIA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>19/07/2021</t>
+          <t>30/03/1956</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,22 +7794,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>92468805</t>
+          <t>92222558</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PIORI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GAMARRA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LUZ ADRIANA</t>
+          <t>SHUNAXHI SUSEJ</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>28/07/2021</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,45 +7857,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>94498440</t>
+          <t>80581038</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PIZANGO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SHAMPIRI</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DAVID YAISON</t>
+          <t>ARMILDA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>27/04/2025</t>
+          <t>23/11/1977</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,22 +7920,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>71748491</t>
+          <t>41898437</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PLAZA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>JOSEPH RICHARD</t>
+          <t>MELVIN ANGEL</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>22/10/2000</t>
+          <t>27/01/1983</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,45 +7983,45 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>92193866</t>
+          <t>75313928</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>GERARD THIAGO</t>
+          <t>DAMMARO LUCERO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>19/07/2005</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>41991155</t>
+          <t>91689899</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>PUENTE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ALFREDO GRIMALDO</t>
+          <t>EDRICK LEODAD JHONNY</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>09/12/1981</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>60409386</t>
+          <t>92464778</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>CHIMANCA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>JHAFFET GERALDO</t>
+          <t>ELFREN HONLY</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>04/07/2006</t>
+          <t>19/07/2021</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,45 +8172,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>70469034</t>
+          <t>92468805</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>GAMARRA</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SANDRO WUILY</t>
+          <t>LUZ ADRIANA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>19/02/2001</t>
+          <t>28/07/2021</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,45 +8235,45 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>47902175</t>
+          <t>94498440</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>SHAMPIRI</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MARIA DE JESUS ELVIA</t>
+          <t>DAVID YAISON</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>07/01/1988</t>
+          <t>27/04/2025</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>92236279</t>
+          <t>71748491</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ROSPIGLIOSI</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OLAYA</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NEYER MEYER</t>
+          <t>JOSEPH RICHARD</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,21 +8322,21 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>22/10/2000</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,45 +8361,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>61256292</t>
+          <t>92193866</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AZUMI YUYIN KAROL</t>
+          <t>GERARD THIAGO</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>23/05/2007</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,40 +8424,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>91996488</t>
+          <t>41991155</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SACCSA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ASHLY TERESA</t>
+          <t>ALFREDO GRIMALDO</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>01/09/2020</t>
+          <t>09/12/1981</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,35 +8487,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>70737398</t>
+          <t>60409386</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>RICRA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
           <t>SALAZAR</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>HUAMAN</t>
-        </is>
-      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NEMERLY KEYLA</t>
+          <t>JHAFFET GERALDO</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>08/05/2007</t>
+          <t>04/07/2006</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>44404892</t>
+          <t>70469034</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LUIS MANUEL</t>
+          <t>SANDRO WUILY</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>30/06/1985</t>
+          <t>19/02/2001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,22 +8613,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>73962347</t>
+          <t>47902175</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SALHUANA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>CAMILA ALEJANDRA</t>
+          <t>MARIA DE JESUS ELVIA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8637,11 +8637,11 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>08/12/1996</t>
+          <t>07/01/1988</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21001701</t>
+          <t>92236279</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>ROSPIGLIOSI</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>OLAYA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>NEYER MEYER</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>21/04/1972</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,22 +8739,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>48423925</t>
+          <t>94421184</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ALANYA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>RICHARD RONALD</t>
+          <t>ALFONSO BENJAMIN</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8763,21 +8763,21 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>08/01/1993</t>
+          <t>19/10/2025</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,45 +8802,45 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>94521679</t>
+          <t>61256292</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>AZUMI YUYIN KAROL</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>18/01/2026</t>
+          <t>23/05/2007</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,22 +8865,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>76320981</t>
+          <t>91996488</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SACCSA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DEYSI LUZCLARITA</t>
+          <t>ASHLY TERESA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8889,16 +8889,16 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>26/12/2001</t>
+          <t>01/09/2020</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,45 +8928,45 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>91994097</t>
+          <t>70737398</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SANTISTEBAN</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CAMILO GABRIEL</t>
+          <t>NEMERLY KEYLA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>08/05/2007</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,22 +8991,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>92655755</t>
+          <t>44404892</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GAEL GABRIEL</t>
+          <t>LUIS MANUEL</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,21 +9015,21 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>27/07/2021</t>
+          <t>30/06/1985</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>76401299</t>
+          <t>73962347</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SALHUANA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CARNICA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AQUILA CIELO</t>
+          <t>CAMILA ALEJANDRA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,16 +9078,16 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>05/04/2002</t>
+          <t>08/12/1996</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,45 +9117,45 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>92216101</t>
+          <t>21001701</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ANTONELA</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>21/04/1972</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,45 +9180,45 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>92450307</t>
+          <t>48423925</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SEGUNDO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>ALANYA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ANALY YANIRA</t>
+          <t>RICHARD RONALD</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>08/01/1993</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,35 +9243,35 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>92471551</t>
+          <t>94521679</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SHAMUYA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MAILY KASUMI</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>18/01/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9306,40 +9306,40 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>44606371</t>
+          <t>76320981</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SINCHE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>JOSE ANGEL</t>
+          <t>DEYSI LUZCLARITA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>13/09/1986</t>
+          <t>26/12/2001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9369,45 +9369,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>73441118</t>
+          <t>91994097</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SORIANO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>SANTISTEBAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NATALI VANESSA</t>
+          <t>CAMILO GABRIEL</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>08/10/1996</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9432,45 +9432,45 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>48477472</t>
+          <t>82244901</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BARJA</t>
+          <t>ÑACO</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LUIS MIGUEL</t>
+          <t>ALISON DANUSKA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>08/12/1993</t>
+          <t>29/09/2021</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9495,35 +9495,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>91993771</t>
+          <t>92655755</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CARHUAMACA</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>BLANCA ABIGAIL</t>
+          <t>GAEL GABRIEL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>27/07/2021</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9558,22 +9558,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>92445123</t>
+          <t>76401299</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SUMAYLLO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CANCHANYA</t>
+          <t>CARNICA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DAYANA SAMANTHA</t>
+          <t>AQUILA CIELO</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9582,21 +9582,21 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>05/04/2002</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9621,45 +9621,45 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>62391082</t>
+          <t>92216101</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TABRA</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>JOSUE BEQUER</t>
+          <t>ANTONELA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>22/07/2007</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9684,22 +9684,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>91688446</t>
+          <t>92450307</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>SEGUNDO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TAYPE</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>BRISEIDA REYNA</t>
+          <t>ANALY YANIRA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>19/01/2020</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>19/01/2025</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9747,35 +9747,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>91812793</t>
+          <t>92471551</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TENAZOA</t>
+          <t>SHAMUYA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NINA</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ABNER ANTOÑIO</t>
+          <t>MAILY KASUMI</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>13/04/2020</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,40 +9810,40 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>61056507</t>
+          <t>44606371</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SINCHE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MAYLITH MELIZA</t>
+          <t>JOSE ANGEL</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>26/03/2001</t>
+          <t>13/09/1986</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,45 +9873,45 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>94562648</t>
+          <t>73441118</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SORIANO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>IAN DARKIEL</t>
+          <t>NATALI VANESSA</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>08/10/1996</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,40 +9936,40 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>92078620</t>
+          <t>48477472</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TUPIÑO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>BARJA</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ALIZEE MIA LIA</t>
+          <t>LUIS MIGUEL</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>25/10/2020</t>
+          <t>08/12/1993</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,45 +9999,45 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>44002317</t>
+          <t>91993771</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UMPIQUIRI</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MAXIMO</t>
+          <t>CARHUAMACA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO</t>
+          <t>BLANCA ABIGAIL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>06/01/1987</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,22 +10062,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>44869785</t>
+          <t>92445123</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>SUMAYLLO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>CANCHANYA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>MARGARITA ELIZABETH</t>
+          <t>DAYANA SAMANTHA</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10086,21 +10086,21 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>05/02/1988</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,22 +10125,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>92319511</t>
+          <t>62391082</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>TABRA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AXEL RAYAN</t>
+          <t>JOSUE BEQUER</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10149,21 +10149,21 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>17/04/2021</t>
+          <t>22/07/2007</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,35 +10188,35 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>92319692</t>
+          <t>91688446</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>TAYPE</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ALVARO MARIANO</t>
+          <t>BRISEIDA REYNA</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>17/04/2021</t>
+          <t>19/01/2020</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/01/2025</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,22 +10251,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>91689659</t>
+          <t>91812793</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TENAZOA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>JAYO</t>
+          <t>NINA</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>GIANNI SEBASTIAN</t>
+          <t>ABNER ANTOÑIO</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>13/04/2020</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,40 +10314,40 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>48389861</t>
+          <t>61056507</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>BILL CLINTON</t>
+          <t>MAYLITH MELIZA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>22/01/1993</t>
+          <t>26/03/2001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,22 +10377,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>76669305</t>
+          <t>94562648</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>IAN DARKIEL</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10401,21 +10401,21 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>07/04/2000</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,22 +10440,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>91897894</t>
+          <t>92078620</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>VILLANTOY</t>
+          <t>TUPIÑO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PRIYA MARBY</t>
+          <t>ALIZEE MIA LIA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>25/10/2020</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,45 +10503,45 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>92451044</t>
+          <t>44002317</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>VILLAS</t>
+          <t>UMPIQUIRI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ROFINO</t>
+          <t>MAXIMO</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ARIELA ARELIS</t>
+          <t>MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>06/01/1987</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,22 +10566,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>91688260</t>
+          <t>44869785</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ZEGARRA</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>LACMA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LUZ ESTRELLA</t>
+          <t>MARGARITA ELIZABETH</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>19/01/2020</t>
+          <t>05/02/1988</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>19/01/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,63 +10629,693 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>92492618</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>URCUCULLAY</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AMES</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>YAMELEY KEIRA</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>5</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>14/08/2021</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>92319511</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>AXEL RAYAN</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>5</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>17/04/2021</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>92319692</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>HUAMAN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ALVARO MARIANO</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>5</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>17/04/2021</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>91689659</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>JAYO</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>GIANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>6</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20/01/2020</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>20/01/2025</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>48389861</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ALIAGA</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BILL CLINTON</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>33</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>22/01/1993</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>76669305</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>JHON</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>26</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>07/04/2000</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>91897894</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>VILLANTOY</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PAUCARCAJA</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PRIYA MARBY</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>6</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>19/06/2020</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>19/06/2025</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>92451044</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>VILLAS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ROFINO</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ARIELA ARELIS</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>5</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>16/07/2021</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M170" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>91688260</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ZEGARRA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>LACMA</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LUZ ESTRELLA</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>6</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>19/01/2020</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>19/01/2025</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M171" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t>92040235</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>ZUMAETA</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>VELASQUEZ</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>DAYL KIM</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F163" t="n">
+      <c r="F172" t="n">
         <v>6</v>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>30/09/2020</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M163" t="n">
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M172" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>94762442</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ÑACO</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SACARIAS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>MERY LARICO</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M173" t="n">
         <v>120604</v>
       </c>
     </row>

--- a/exports/34721_lurinchincha.xlsx
+++ b/exports/34721_lurinchincha.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1431,45 +1431,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>94738019</t>
+          <t>76293885</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASTO</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GOSME</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FREY ERLING DARIEL</t>
+          <t>JOSELYN MARDHELY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>14/02/2006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,40 +1494,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>76293885</t>
+          <t>43158719</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JOSELYN MARDHELY</t>
+          <t>NICOLAIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14/02/2006</t>
+          <t>14/08/1985</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1557,40 +1557,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>43158719</t>
+          <t>75626359</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>AURIS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>BILLAVERDE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NICOLAIN</t>
+          <t>CARLA VALERIA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14/08/1985</t>
+          <t>18/09/2000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,45 +1620,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>75626359</t>
+          <t>94343751</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AURIS</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BILLAVERDE</t>
+          <t>MALLASCA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CARLA VALERIA</t>
+          <t>LIAM GAEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/09/2000</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>13/08/2025</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,22 +1683,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>94343751</t>
+          <t>91966118</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MALLASCA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LIAM GAEL</t>
+          <t>LUIS CHARLES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>09/08/2020</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13/08/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,22 +1746,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>91966118</t>
+          <t>71205808</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>MUENA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LUIS CHARLES</t>
+          <t>LEANDRO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1770,16 +1770,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>09/08/2020</t>
+          <t>01/05/1996</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1935,22 +1935,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>92507704</t>
+          <t>94678867</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BRAMA</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DELSY ROSMERI</t>
+          <t>YASURI ROSITA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1959,11 +1959,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23/08/2021</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>94678867</t>
+          <t>74282565</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2008,35 +2008,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>OROSCO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>YASURI ROSITA</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>04/10/1999</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,22 +2061,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>74282565</t>
+          <t>46048783</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>CACHIQUE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OROSCO</t>
+          <t>MERMAO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>DANY BLAIR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>04/10/1999</t>
+          <t>21/10/1989</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,45 +2124,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>46048783</t>
+          <t>81912306</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CACHIQUE</t>
+          <t>CAHUIN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MERMAO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DANY BLAIR</t>
+          <t>AINHOA ALISSANDRA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21/10/1989</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,45 +2187,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>81912306</t>
+          <t>20027289</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CAHUIN</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AINHOA ALISSANDRA</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>15/01/1968</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20027289</t>
+          <t>92149750</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2260,35 +2260,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>JENNIFER ANDREA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15/01/1968</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,27 +2313,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>92149750</t>
+          <t>91992750</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CALLE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JENNIFER ANDREA</t>
+          <t>JACOB</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,35 +2376,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>91992750</t>
+          <t>92444536</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CALLE</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MUNIVE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JACOB</t>
+          <t>VELIANKA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,35 +2439,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>92444536</t>
+          <t>91897651</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CASIMIRO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MUNIVE</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VELIANKA</t>
+          <t>ELVIN YEIKO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,45 +2502,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>74977236</t>
+          <t>94539160</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CANCHARI</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ANIBAL JULHIÑO</t>
+          <t>BRIANA AMELIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17/03/2002</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11/06/2013</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>91897651</t>
+          <t>72897620</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASIMIRO</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ELVIN YEIKO</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>07/11/1996</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,22 +2628,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>94539160</t>
+          <t>60948581</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BRIANA AMELIA</t>
+          <t>STEPHANIE MISHELLE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>19/04/2001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,22 +2691,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>72897620</t>
+          <t>41891670</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>WALTER HUGO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>07/11/1996</t>
+          <t>08/06/1982</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>60948581</t>
+          <t>94670548</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,35 +2764,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>STEPHANIE MISHELLE</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/04/2001</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,22 +2817,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>41891670</t>
+          <t>94295173</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CATEÑO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>WALTER HUGO</t>
+          <t>JHON WILLIAMS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>08/06/1982</t>
+          <t>02/08/2017</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,35 +2880,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>94670548</t>
+          <t>94356549</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>ZEINEP ABIGAIL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>22/08/2025</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,22 +2943,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>94295173</t>
+          <t>93985686</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CATEÑO</t>
+          <t>CCOICCA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>EVANGELISTA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JHON WILLIAMS</t>
+          <t>GAEL ALEXANDER</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>02/08/2017</t>
+          <t>23/09/2024</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,22 +3006,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>94356549</t>
+          <t>81912333</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CCORAHUA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>MAYHUA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ZEINEP ABIGAIL</t>
+          <t>BELEN YAMILETH</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3030,11 +3030,11 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>22/08/2025</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,22 +3069,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>93985686</t>
+          <t>94220420</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CCOICCA</t>
+          <t>CELSO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVANGELISTA</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GAEL ALEXANDER</t>
+          <t>ETHAN ALDO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23/09/2024</t>
+          <t>22/04/2025</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,22 +3132,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>81912333</t>
+          <t>91883722</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CCORAHUA</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MAYHUA</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BELEN YAMILETH</t>
+          <t>SAYNETH JHOANNA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3156,11 +3156,11 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,22 +3195,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>94220420</t>
+          <t>91898061</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CELSO</t>
+          <t>CHAVARRIAS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ETHAN ALDO</t>
+          <t>ZENDER LIAN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3219,11 +3219,11 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22/04/2025</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,35 +3258,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>91883722</t>
+          <t>94241992</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>DE LA FUENTE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAYNETH JHOANNA</t>
+          <t>ANGELO EZEQUIEL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>91898061</t>
+          <t>91754386</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHAVARRIAS</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ZENDER LIAN</t>
+          <t>DEID ALEXANDER</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,35 +3384,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>94241992</t>
+          <t>92321088</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>CHUMPATI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DE LA FUENTE</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ANGELO EZEQUIEL</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>18/04/2021</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,40 +3447,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>92456436</t>
+          <t>44503468</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>CHUMPE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ANDREA ROCIO</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20/07/2021</t>
+          <t>08/02/1983</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,45 +3510,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>91754386</t>
+          <t>77503900</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>COLACHAGUA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DEID ALEXANDER</t>
+          <t>SHEILA LETICIA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>08/10/1995</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>92321088</t>
+          <t>92039400</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CHUMPATI</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>CAÑARI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ROSA</t>
+          <t>AZUMI SHANTAL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18/04/2021</t>
+          <t>29/09/2020</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,40 +3636,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>44503468</t>
+          <t>71718570</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHUMPE</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>GALA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>PATSI CINTHIA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>08/02/1983</t>
+          <t>05/02/2001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,35 +3699,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>77503900</t>
+          <t>46791163</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COLACHAGUA</t>
+          <t>COTERA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SHEILA LETICIA</t>
+          <t>RODIL RENE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>08/10/1995</t>
+          <t>16/12/1990</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,22 +3762,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>92039400</t>
+          <t>00092715</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CUEVA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CAÑARI</t>
+          <t>RICOPA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AZUMI SHANTAL</t>
+          <t>ROSA MERY</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>29/09/2020</t>
+          <t>07/06/1971</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,45 +3825,45 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>71718570</t>
+          <t>92446495</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>DAHUA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GALA</t>
+          <t>RUPAY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PATSI CINTHIA</t>
+          <t>DEYVI JACK</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>05/02/2001</t>
+          <t>13/07/2021</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,45 +3888,45 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>75287007</t>
+          <t>94396233</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>DEXTRE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ENERO</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KETTY DOMINICA</t>
+          <t>GAEL KAYRO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>30/09/1999</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>46791163</t>
+          <t>92207811</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COTERA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RODIL RENE</t>
+          <t>ERIK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>16/12/1990</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,45 +4014,45 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00092715</t>
+          <t>92222315</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CUEVA</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RICOPA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ROSA MERY</t>
+          <t>ABDIEL JAZIEL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>07/06/1971</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,45 +4077,45 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>92446495</t>
+          <t>42413512</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DAHUA</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RUPAY</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DEYVI JACK</t>
+          <t>JAZMIN BETZABETH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>13/07/2021</t>
+          <t>11/05/1984</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,35 +4140,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>94396233</t>
+          <t>92489713</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DEXTRE</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GAEL KAYRO</t>
+          <t>INGRID ASTRID</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,40 +4203,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>92207811</t>
+          <t>75318534</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ERIK</t>
+          <t>ARISBEL ARIANA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>09/04/2006</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>92222315</t>
+          <t>76156896</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>EUSTAQUIO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>BENITES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ABDIEL JAZIEL</t>
+          <t>JAVIER</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>09/07/1999</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4329,22 +4329,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>42413512</t>
+          <t>92194218</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ESPINO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JAZMIN BETZABETH</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,21 +4353,21 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11/05/1984</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,27 +4392,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>92489713</t>
+          <t>92222175</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PORTOCARRERO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>INGRID ASTRID</t>
+          <t>SAMIR MILER</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,40 +4455,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>75318534</t>
+          <t>42214488</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ARISBEL ARIANA</t>
+          <t>JAIME TEOFILO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09/04/2006</t>
+          <t>12/08/1982</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,45 +4518,45 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>76156896</t>
+          <t>94642996</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EUSTAQUIO</t>
+          <t>GASTELU</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BENITES</t>
+          <t>CABEZAS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JAVIER</t>
+          <t>ABIGAIL MEDALI</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>09/07/1999</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,35 +4581,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>92194218</t>
+          <t>94445786</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ESPINO</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>CLEIDER</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,22 +4644,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>92222175</t>
+          <t>91885374</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GUEROVICH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PORTOCARRERO</t>
+          <t>ARANCEL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SAMIR MILER</t>
+          <t>ADRIEL JORGE</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,11 +4668,11 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>09/06/2020</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,22 +4707,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>42214488</t>
+          <t>75101251</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GUILLEN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JAIME TEOFILO</t>
+          <t>ELMER</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>12/08/1982</t>
+          <t>14/01/2001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,22 +4770,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>94642996</t>
+          <t>20996386</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GASTELU</t>
+          <t>HUAMANCHAHUA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CABEZAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ABIGAIL MEDALI</t>
+          <t>FRICIA ELIZABETH</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4794,21 +4794,21 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>02/06/1971</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,35 +4833,35 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>94445786</t>
+          <t>94047252</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>HUANICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CLEIDER</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,45 +4896,45 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>91885374</t>
+          <t>78765946</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GUEROVICH</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ARANCEL</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ADRIEL JORGE</t>
+          <t>YARISLEY DAFNE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>09/06/2020</t>
+          <t>24/08/2014</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,27 +4959,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>75101251</t>
+          <t>70809810</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GUILLEN</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ELMER</t>
+          <t>JAQUELINE MAYUMI</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14/01/2001</t>
+          <t>15/08/2001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>76918087</t>
+          <t>92445032</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GUIZADO</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RANDY</t>
+          <t>LINDA YEIS</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>05/02/1998</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,35 +5085,35 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20996386</t>
+          <t>42901772</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HUAMANCHAHUA</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FRICIA ELIZABETH</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>02/06/1971</t>
+          <t>06/08/1982</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,35 +5148,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>94047252</t>
+          <t>92082689</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HUANICO</t>
+          <t>LANAZCA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>SIERRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>JORGE ALEJANDRO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>28/10/2020</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5211,40 +5211,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>78765946</t>
+          <t>75001764</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>YARISLEY DAFNE</t>
+          <t>LUIGUI DANIEL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>24/08/2014</t>
+          <t>13/04/2001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,35 +5274,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>70809810</t>
+          <t>76412062</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JAQUELINE MAYUMI</t>
+          <t>SERGIO RAFAEL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>15/08/2001</t>
+          <t>14/11/2003</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,27 +5337,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>92445032</t>
+          <t>92193263</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>LIMACHE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LINDA YEIS</t>
+          <t>IKER NOAH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>42901772</t>
+          <t>20580064</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>LLANCACHAGUA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>HUACCHO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>JORGE PAPA</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,16 +5424,16 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>06/08/1982</t>
+          <t>23/06/1944</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,35 +5463,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>92082689</t>
+          <t>92469548</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LANAZCA</t>
+          <t>LOZADA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SIERRA</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JORGE ALEJANDRO</t>
+          <t>CATALEYA ZEYNEP</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>28/10/2020</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,40 +5526,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>75001764</t>
+          <t>43511339</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ECHABAUDES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LUIGUI DANIEL</t>
+          <t>DAYSY</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13/04/2001</t>
+          <t>19/12/1985</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,45 +5589,45 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>76412062</t>
+          <t>94615934</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>MALVEÑO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SERGIO RAFAEL</t>
+          <t>MAYURI</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14/11/2003</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>92193263</t>
+          <t>70606096</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LIMACHE</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>IKER NOAH</t>
+          <t>PERCY JESUS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>05/08/1998</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20580064</t>
+          <t>94618669</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LLANCACHAGUA</t>
+          <t>MATA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HUACCHO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JORGE PAPA</t>
+          <t>EMIR RUBEN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>23/06/1944</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,35 +5778,35 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>92469548</t>
+          <t>92039861</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LOZADA</t>
+          <t>MATENCIOS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CATALEYA ZEYNEP</t>
+          <t>JHASTIN YANDEL</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>30/09/2020</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>43511339</t>
+          <t>94307754</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>MAYBANTI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ECHABAUDES</t>
+          <t>ÑACO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DAYSY</t>
+          <t>MEDALY ESTHER</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19/12/1985</t>
+          <t>09/07/2025</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,22 +5904,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>94615934</t>
+          <t>92194352</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MALVEÑO</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MAYURI</t>
+          <t>PILAR INGRID</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5928,11 +5928,11 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,22 +5967,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>70606096</t>
+          <t>77016635</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PERCY JESUS</t>
+          <t>BERRY</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5991,11 +5991,11 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>05/08/1998</t>
+          <t>19/11/2001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,22 +6030,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>94618669</t>
+          <t>76321000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MATA</t>
+          <t>MELGAREJO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EMIR RUBEN</t>
+          <t>LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6054,21 +6054,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>14/12/2001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,22 +6093,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>92039861</t>
+          <t>47211525</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MATENCIOS</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>BELLIDO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>JHASTIN YANDEL</t>
+          <t>MARCIAL LINDO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,21 +6117,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>30/09/2020</t>
+          <t>03/03/1991</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>94307754</t>
+          <t>77042300</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAYBANTI</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ÑACO</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MEDALY ESTHER</t>
+          <t>JENNIFER PILAR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>01/08/2005</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>92194352</t>
+          <t>77418210</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MERINO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>ENCISO</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PILAR INGRID</t>
+          <t>JUDITH</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,21 +6243,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>28/02/1999</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,45 +6282,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>77016635</t>
+          <t>92040429</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BERRY</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>19/11/2001</t>
+          <t>30/09/2020</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,22 +6345,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>76321000</t>
+          <t>41594775</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MELGAREJO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE</t>
+          <t>HERNAN</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6369,16 +6369,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>14/12/2001</t>
+          <t>25/10/1982</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,45 +6408,45 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>47211525</t>
+          <t>92192495</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BELLIDO</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MARCIAL LINDO</t>
+          <t>ALESSIA YATZIRI</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>03/03/1991</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,22 +6471,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>74281497</t>
+          <t>47760020</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MUNGUI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ATAPOMA</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ELDER MESIAS</t>
+          <t>CLEVER</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,11 +6495,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>12/07/1995</t>
+          <t>19/10/1989</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>77042300</t>
+          <t>92911456</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MURAYARI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>LOZANO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>JENNIFER PILAR</t>
+          <t>YARITZA ITZEL</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>01/08/2005</t>
+          <t>29/05/2022</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,35 +6597,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>77418210</t>
+          <t>76927877</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MERINO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ENCISO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>JUDITH</t>
+          <t>JUAN DAVID</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>28/02/1999</t>
+          <t>06/04/2006</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,35 +6660,35 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>92040429</t>
+          <t>94682414</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>RONY CESAR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>30/09/2020</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>41594775</t>
+          <t>94398586</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>HERNAN</t>
+          <t>ZHENYI KENYI</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>25/10/1982</t>
+          <t>28/09/2025</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>92192495</t>
+          <t>91883930</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>HUAYA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ALESSIA YATZIRI</t>
+          <t>ARIANA AMELY</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,35 +6849,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>47760020</t>
+          <t>46449555</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MUNGUI</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ZACARIAS</t>
+          <t>BRAÑES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CLEVER</t>
+          <t>NADIA TANIA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>19/10/1989</t>
+          <t>28/04/1990</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>92911456</t>
+          <t>41517689</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MURAYARI</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LOZANO</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>YARITZA ITZEL</t>
+          <t>NILDA YANET</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>29/05/2022</t>
+          <t>15/10/1982</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>76927877</t>
+          <t>92489139</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>OSORES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LLAMUCO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JUAN DAVID</t>
+          <t>IAN KARPER</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>06/04/2006</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,22 +7038,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>94682414</t>
+          <t>92087755</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RONY CESAR</t>
+          <t>ALFONSO BRANT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>31/10/2020</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>94398586</t>
+          <t>91885525</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>PACHIRI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ZACARIAS</t>
+          <t>CAYETANO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ZHENYI KENYI</t>
+          <t>JUAN BENJAMIN</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,11 +7125,11 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>28/09/2025</t>
+          <t>09/06/2020</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,35 +7164,35 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>91883930</t>
+          <t>94191376</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>PAIMA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HUAYA</t>
+          <t>QUENTISHA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ARIANA AMELY</t>
+          <t>LIAM MAIKEL</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,45 +7227,45 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>46449555</t>
+          <t>92451937</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BRAÑES</t>
+          <t>HUARACC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NADIA TANIA</t>
+          <t>NEHEMIAS RICHARD</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>28/04/1990</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,22 +7290,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>41517689</t>
+          <t>82244708</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>PATRICIO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>SANTOMA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NILDA YANET</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>15/10/1982</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,45 +7353,45 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>92489139</t>
+          <t>49103748</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OSORES</t>
+          <t>PICHUCA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LLAMUCO</t>
+          <t>PIUNCA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>IAN KARPER</t>
+          <t>HILARIA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>30/03/1956</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,35 +7416,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>92087755</t>
+          <t>92222558</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>PIORI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ALFONSO BRANT</t>
+          <t>SHUNAXHI SUSEJ</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>31/10/2020</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,45 +7479,45 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>91885525</t>
+          <t>80581038</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PACHIRI</t>
+          <t>PIZANGO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CAYETANO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>JUAN BENJAMIN</t>
+          <t>ARMILDA</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>09/06/2020</t>
+          <t>23/11/1977</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,22 +7542,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>94191376</t>
+          <t>41898437</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PAIMA</t>
+          <t>PLAZA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>QUENTISHA</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LIAM MAIKEL</t>
+          <t>MELVIN ANGEL</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>27/01/1983</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>92451937</t>
+          <t>75313928</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HUARACC</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NEHEMIAS RICHARD</t>
+          <t>DAMMARO LUCERO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>19/07/2005</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,35 +7668,35 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>82244708</t>
+          <t>91689899</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PATRICIO</t>
+          <t>PUENTE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SANTOMA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>EDRICK LEODAD JHONNY</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,45 +7731,45 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>49103748</t>
+          <t>92464778</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PICHUCA</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PIUNCA</t>
+          <t>CHIMANCA</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>HILARIA</t>
+          <t>ELFREN HONLY</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>30/03/1956</t>
+          <t>19/07/2021</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,22 +7794,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>92222558</t>
+          <t>92468805</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PIORI</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GAMARRA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SHUNAXHI SUSEJ</t>
+          <t>LUZ ADRIANA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>28/07/2021</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,45 +7857,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>80581038</t>
+          <t>94498440</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PIZANGO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>SHAMPIRI</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ARMILDA</t>
+          <t>DAVID YAISON</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>23/11/1977</t>
+          <t>27/04/2025</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,22 +7920,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>41898437</t>
+          <t>71748491</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PLAZA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MELVIN ANGEL</t>
+          <t>JOSEPH RICHARD</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>27/01/1983</t>
+          <t>22/10/2000</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,45 +7983,45 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>75313928</t>
+          <t>92193866</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DAMMARO LUCERO</t>
+          <t>GERARD THIAGO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>19/07/2005</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>91689899</t>
+          <t>41991155</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PUENTE</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EDRICK LEODAD JHONNY</t>
+          <t>ALFREDO GRIMALDO</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>09/12/1981</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>92464778</t>
+          <t>60409386</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CHIMANCA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ELFREN HONLY</t>
+          <t>JHAFFET GERALDO</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>19/07/2021</t>
+          <t>04/07/2006</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,45 +8172,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>92468805</t>
+          <t>70469034</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GAMARRA</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LUZ ADRIANA</t>
+          <t>SANDRO WUILY</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>28/07/2021</t>
+          <t>19/02/2001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,45 +8235,45 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>94498440</t>
+          <t>47902175</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SHAMPIRI</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DAVID YAISON</t>
+          <t>MARIA DE JESUS ELVIA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>27/04/2025</t>
+          <t>07/01/1988</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>71748491</t>
+          <t>92236279</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ROSPIGLIOSI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>OLAYA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>JOSEPH RICHARD</t>
+          <t>NEYER MEYER</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,21 +8322,21 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>22/10/2000</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,45 +8361,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>92193866</t>
+          <t>61256292</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GERARD THIAGO</t>
+          <t>AZUMI YUYIN KAROL</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>23/05/2007</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,40 +8424,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>41991155</t>
+          <t>91996488</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>SACCSA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ALFREDO GRIMALDO</t>
+          <t>ASHLY TERESA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>09/12/1981</t>
+          <t>01/09/2020</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,35 +8487,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>60409386</t>
+          <t>70737398</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>JHAFFET GERALDO</t>
+          <t>NEMERLY KEYLA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>04/07/2006</t>
+          <t>08/05/2007</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>70469034</t>
+          <t>44404892</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SANDRO WUILY</t>
+          <t>LUIS MANUEL</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>19/02/2001</t>
+          <t>30/06/1985</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,22 +8613,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>47902175</t>
+          <t>73962347</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>SALHUANA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MARIA DE JESUS ELVIA</t>
+          <t>CAMILA ALEJANDRA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8637,11 +8637,11 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>07/01/1988</t>
+          <t>08/12/1996</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>92236279</t>
+          <t>21001701</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ROSPIGLIOSI</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>OLAYA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NEYER MEYER</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>21/04/1972</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,22 +8739,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>94421184</t>
+          <t>48423925</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ALANYA</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ALFONSO BENJAMIN</t>
+          <t>RICHARD RONALD</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8763,21 +8763,21 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>08/01/1993</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,45 +8802,45 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>61256292</t>
+          <t>94521679</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AZUMI YUYIN KAROL</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>23/05/2007</t>
+          <t>18/01/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,22 +8865,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>91996488</t>
+          <t>76320981</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SACCSA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ASHLY TERESA</t>
+          <t>DEYSI LUZCLARITA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8889,16 +8889,16 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>01/09/2020</t>
+          <t>26/12/2001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,45 +8928,45 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>70737398</t>
+          <t>91994097</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>SANTISTEBAN</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NEMERLY KEYLA</t>
+          <t>CAMILO GABRIEL</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>08/05/2007</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,22 +8991,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>44404892</t>
+          <t>92655755</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LUIS MANUEL</t>
+          <t>GAEL GABRIEL</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,21 +9015,21 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>30/06/1985</t>
+          <t>27/07/2021</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>73962347</t>
+          <t>76401299</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SALHUANA</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>CARNICA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CAMILA ALEJANDRA</t>
+          <t>AQUILA CIELO</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,16 +9078,16 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>08/12/1996</t>
+          <t>05/04/2002</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,45 +9117,45 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>21001701</t>
+          <t>92216101</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>ANTONELA</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>21/04/1972</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,45 +9180,45 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>48423925</t>
+          <t>92450307</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SEGUNDO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ALANYA</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RICHARD RONALD</t>
+          <t>ANALY YANIRA</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>08/01/1993</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,35 +9243,35 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>94521679</t>
+          <t>92471551</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SHAMUYA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>MAILY KASUMI</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>18/01/2026</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9306,40 +9306,40 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>76320981</t>
+          <t>44606371</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SINCHE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>DEYSI LUZCLARITA</t>
+          <t>JOSE ANGEL</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>26/12/2001</t>
+          <t>13/09/1986</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9369,45 +9369,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>91994097</t>
+          <t>73441118</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SORIANO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SANTISTEBAN</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CAMILO GABRIEL</t>
+          <t>NATALI VANESSA</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>08/10/1996</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9432,45 +9432,45 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>82244901</t>
+          <t>48477472</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ÑACO</t>
+          <t>BARJA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ALISON DANUSKA</t>
+          <t>LUIS MIGUEL</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>29/09/2021</t>
+          <t>08/12/1993</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9495,35 +9495,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>92655755</t>
+          <t>91993771</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>CARHUAMACA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GAEL GABRIEL</t>
+          <t>BLANCA ABIGAIL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>27/07/2021</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9558,22 +9558,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>76401299</t>
+          <t>92445123</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SUMAYLLO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CARNICA</t>
+          <t>CANCHANYA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>AQUILA CIELO</t>
+          <t>DAYANA SAMANTHA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9582,21 +9582,21 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>05/04/2002</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9621,45 +9621,45 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>92216101</t>
+          <t>62391082</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>TABRA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ANTONELA</t>
+          <t>JOSUE BEQUER</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>22/07/2007</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9684,22 +9684,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>92450307</t>
+          <t>91688446</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SEGUNDO</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>TAYPE</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ANALY YANIRA</t>
+          <t>BRISEIDA REYNA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>19/01/2020</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>19/01/2025</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9747,35 +9747,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>92471551</t>
+          <t>91812793</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SHAMUYA</t>
+          <t>TENAZOA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>NINA</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MAILY KASUMI</t>
+          <t>ABNER ANTOÑIO</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>13/04/2020</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,40 +9810,40 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>44606371</t>
+          <t>61056507</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SINCHE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>JOSE ANGEL</t>
+          <t>MAYLITH MELIZA</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>13/09/1986</t>
+          <t>26/03/2001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,45 +9873,45 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>73441118</t>
+          <t>94562648</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SORIANO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NATALI VANESSA</t>
+          <t>IAN DARKIEL</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>08/10/1996</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,40 +9936,40 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>48477472</t>
+          <t>92078620</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TUPIÑO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BARJA</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LUIS MIGUEL</t>
+          <t>ALIZEE MIA LIA</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>08/12/1993</t>
+          <t>25/10/2020</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,45 +9999,45 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>91993771</t>
+          <t>44002317</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>UMPIQUIRI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CARHUAMACA</t>
+          <t>MAXIMO</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>BLANCA ABIGAIL</t>
+          <t>MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>06/01/1987</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,22 +10062,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>92445123</t>
+          <t>44869785</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SUMAYLLO</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CANCHANYA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DAYANA SAMANTHA</t>
+          <t>MARGARITA ELIZABETH</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10086,21 +10086,21 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>05/02/1988</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,22 +10125,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>62391082</t>
+          <t>92319511</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TABRA</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>JOSUE BEQUER</t>
+          <t>AXEL RAYAN</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10149,21 +10149,21 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22/07/2007</t>
+          <t>17/04/2021</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,35 +10188,35 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>91688446</t>
+          <t>92319692</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TAYPE</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>BRISEIDA REYNA</t>
+          <t>ALVARO MARIANO</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>19/01/2020</t>
+          <t>17/04/2021</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>19/01/2025</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,22 +10251,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>91812793</t>
+          <t>91689659</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TENAZOA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NINA</t>
+          <t>JAYO</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ABNER ANTOÑIO</t>
+          <t>GIANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>13/04/2020</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,40 +10314,40 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>61056507</t>
+          <t>48389861</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>MAYLITH MELIZA</t>
+          <t>BILL CLINTON</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>26/03/2001</t>
+          <t>22/01/1993</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,22 +10377,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>94562648</t>
+          <t>76669305</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>IAN DARKIEL</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10401,21 +10401,21 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>07/04/2000</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,22 +10440,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>92078620</t>
+          <t>91897894</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TUPIÑO</t>
+          <t>VILLANTOY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>PAUCARCAJA</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ALIZEE MIA LIA</t>
+          <t>PRIYA MARBY</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>25/10/2020</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,45 +10503,45 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>44002317</t>
+          <t>92451044</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>UMPIQUIRI</t>
+          <t>VILLAS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MAXIMO</t>
+          <t>ROFINO</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO</t>
+          <t>ARIELA ARELIS</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>06/01/1987</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,22 +10566,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>44869785</t>
+          <t>91688260</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>ZEGARRA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>LACMA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>MARGARITA ELIZABETH</t>
+          <t>LUZ ESTRELLA</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>05/02/1988</t>
+          <t>19/01/2020</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>19/01/2025</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,22 +10629,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>92492618</t>
+          <t>92040235</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>URCUCULLAY</t>
+          <t>ZUMAETA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>YAMELEY KEIRA</t>
+          <t>DAYL KIM</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10653,11 +10653,11 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>14/08/2021</t>
+          <t>30/09/2020</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10686,636 +10686,6 @@
         </is>
       </c>
       <c r="M163" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>92319511</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>RAMOS</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>AXEL RAYAN</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>5</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>17/04/2021</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M164" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>92319692</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>VARGAS</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>HUAMAN</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>ALVARO MARIANO</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>5</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>17/04/2021</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M165" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>91689659</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>VASQUEZ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>JAYO</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>GIANNI SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>6</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20/01/2020</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>20/01/2025</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M166" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>48389861</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>VEGA</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>ALIAGA</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>BILL CLINTON</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>33</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>22/01/1993</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>05/04/2025</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M167" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>76669305</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>VEGA</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>SALAZAR</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>JHON</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>26</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>07/04/2000</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>10/02/2025</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M168" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>91897894</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>VILLANTOY</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>PAUCARCAJA</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>PRIYA MARBY</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v>6</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>19/06/2020</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>19/06/2025</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M169" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>92451044</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>VILLAS</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>ROFINO</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>ARIELA ARELIS</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>5</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>16/07/2021</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>16/07/2026</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M170" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>91688260</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>ZEGARRA</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>LACMA</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>LUZ ESTRELLA</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>6</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>19/01/2020</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>19/01/2025</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M171" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>92040235</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>ZUMAETA</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>VELASQUEZ</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>DAYL KIM</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>6</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>30/09/2020</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M172" t="n">
-        <v>120604</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>94762442</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>ÑACO</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>SACARIAS</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>MERY LARICO</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M173" t="n">
         <v>120604</v>
       </c>
     </row>

--- a/exports/34721_lurinchincha.xlsx
+++ b/exports/34721_lurinchincha.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,7 +942,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RNF</t>
+          <t>DASHA AILANY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1116,35 +1116,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>92516138</t>
+          <t>94593736</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>ANTENOR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SHINCARI</t>
+          <t>OMIÑAHUANTI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RODRIGO ANTONY</t>
+          <t>MILAGRO MILENY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1179,45 +1179,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>61604339</t>
+          <t>92516138</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APARICIO</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HILARIO</t>
+          <t>SHINCARI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LUCIANA</t>
+          <t>RODRIGO ANTONY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13/04/2007</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>71899838</t>
+          <t>61604339</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APUMAYTA</t>
+          <t>APARICIO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>HILARIO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MILIANA</t>
+          <t>LUCIANA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/06/1998</t>
+          <t>13/04/2007</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,45 +1305,45 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>94628927</t>
+          <t>71899838</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>APUMAYTA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ASHER NADIR</t>
+          <t>MILIANA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>18/06/1998</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1368,22 +1368,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>91688388</t>
+          <t>94628927</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARMACANQUI</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ARON ELISEO</t>
+          <t>ASHER NADIR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19/01/2020</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19/01/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,45 +1431,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>76293885</t>
+          <t>91688388</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>ARMACANQUI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOSELYN MARDHELY</t>
+          <t>ARON ELISEO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14/02/2006</t>
+          <t>19/01/2020</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>19/01/2025</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,22 +1494,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>43158719</t>
+          <t>94738019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>ASTO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GOSME</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NICOLAIN</t>
+          <t>FREY ERLING DARIEL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14/08/1985</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1557,22 +1557,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>75626359</t>
+          <t>76293885</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AURIS</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BILLAVERDE</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CARLA VALERIA</t>
+          <t>JOSELYN MARDHELY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/09/2000</t>
+          <t>14/02/2006</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,22 +1620,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>94343751</t>
+          <t>43158719</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MALLASCA</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LIAM GAEL</t>
+          <t>NICOLAIN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>14/08/1985</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13/08/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,40 +1683,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>91966118</t>
+          <t>75626359</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>AURIS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>BILLAVERDE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LUIS CHARLES</t>
+          <t>CARLA VALERIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>09/08/2020</t>
+          <t>18/09/2000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,22 +1746,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>71205808</t>
+          <t>94343751</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MUENA</t>
+          <t>MALLASCA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>LIAM GAEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01/05/1996</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>13/08/2025</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1809,22 +1809,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>61590719</t>
+          <t>91966118</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BERROSPI</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RICARDO SANSON</t>
+          <t>LUIS CHARLES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1833,16 +1833,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19/05/1996</t>
+          <t>09/08/2020</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1872,22 +1872,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>76059540</t>
+          <t>61590719</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BOZA</t>
+          <t>BERROSPI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>RICARDO SANSON</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,16 +1896,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/05/1998</t>
+          <t>19/05/1996</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,45 +1935,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>94678867</t>
+          <t>76059540</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>BOZA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>YASURI ROSITA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>05/05/1998</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,40 +1998,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>74282565</t>
+          <t>92507704</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>BRAMA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OROSCO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>DELSY ROSMERI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/10/1999</t>
+          <t>23/08/2021</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,45 +2061,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>46048783</t>
+          <t>94678867</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CACHIQUE</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MERMAO</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DANY BLAIR</t>
+          <t>YASURI ROSITA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21/10/1989</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,45 +2124,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>81912306</t>
+          <t>74282565</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CAHUIN</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>OROSCO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AINHOA ALISSANDRA</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>04/10/1999</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,22 +2187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20027289</t>
+          <t>46048783</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CACHIQUE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>MERMAO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>DANY BLAIR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2211,11 +2211,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15/01/1968</t>
+          <t>21/10/1989</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,22 +2250,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>92149750</t>
+          <t>81912306</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CAHUIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JENNIFER ANDREA</t>
+          <t>AINHOA ALISSANDRA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,22 +2313,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>91992750</t>
+          <t>20027289</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CALLE</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JACOB</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>15/01/1968</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>92444536</t>
+          <t>92149750</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MUNIVE</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VELIANKA</t>
+          <t>JENNIFER ANDREA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,11 +2400,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,22 +2439,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>91897651</t>
+          <t>91992750</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASIMIRO</t>
+          <t>CALLE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ELVIN YEIKO</t>
+          <t>JACOB</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,22 +2502,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>94539160</t>
+          <t>92444536</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>MUNIVE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BRIANA AMELIA</t>
+          <t>VELIANKA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2526,11 +2526,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>72897620</t>
+          <t>74977236</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>CANCHARI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>ANIBAL JULHIÑO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>07/11/1996</t>
+          <t>17/03/2002</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>11/06/2013</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,45 +2628,45 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>60948581</t>
+          <t>91897651</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASIMIRO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>STEPHANIE MISHELLE</t>
+          <t>ELVIN YEIKO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19/04/2001</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,45 +2691,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>41891670</t>
+          <t>94539160</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WALTER HUGO</t>
+          <t>BRIANA AMELIA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>08/06/1982</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2754,22 +2754,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>94670548</t>
+          <t>72897620</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2778,21 +2778,21 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>07/11/1996</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,40 +2817,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>94295173</t>
+          <t>60948581</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CATEÑO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JHON WILLIAMS</t>
+          <t>STEPHANIE MISHELLE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>02/08/2017</t>
+          <t>19/04/2001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,45 +2880,45 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>94356549</t>
+          <t>41891670</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ZEINEP ABIGAIL</t>
+          <t>WALTER HUGO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22/08/2025</t>
+          <t>08/06/1982</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,22 +2943,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>93985686</t>
+          <t>94670548</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CCOICCA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EVANGELISTA</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GAEL ALEXANDER</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23/09/2024</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,35 +3006,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>81912333</t>
+          <t>94295173</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CCORAHUA</t>
+          <t>CATEÑO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MAYHUA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BELEN YAMILETH</t>
+          <t>JHON WILLIAMS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>02/08/2017</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,27 +3069,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>94220420</t>
+          <t>94356549</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CELSO</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ETHAN ALDO</t>
+          <t>ZEINEP ABIGAIL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22/04/2025</t>
+          <t>22/08/2025</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,35 +3132,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>91883722</t>
+          <t>93985686</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>CCOICCA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>EVANGELISTA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAYNETH JHOANNA</t>
+          <t>GAEL ALEXANDER</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>23/09/2024</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,35 +3195,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>91898061</t>
+          <t>81912333</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CHAVARRIAS</t>
+          <t>CCORAHUA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MAYHUA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ZENDER LIAN</t>
+          <t>BELEN YAMILETH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>94241992</t>
+          <t>94220420</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>CELSO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DE LA FUENTE</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ANGELO EZEQUIEL</t>
+          <t>ETHAN ALDO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>22/04/2025</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,27 +3321,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>91754386</t>
+          <t>91883722</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DEID ALEXANDER</t>
+          <t>SAYNETH JHOANNA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,35 +3384,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>92321088</t>
+          <t>91898061</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CHUMPATI</t>
+          <t>CHAVARRIAS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ROSA</t>
+          <t>ZENDER LIAN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/04/2021</t>
+          <t>19/06/2020</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>44503468</t>
+          <t>94241992</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CHUMPE</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>DE LA FUENTE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>ANGELO EZEQUIEL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>08/02/1983</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,22 +3510,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>77503900</t>
+          <t>92456436</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COLACHAGUA</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SHEILA LETICIA</t>
+          <t>ANDREA ROCIO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,16 +3534,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>08/10/1995</t>
+          <t>20/07/2021</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,27 +3573,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>92039400</t>
+          <t>91754386</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAÑARI</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AZUMI SHANTAL</t>
+          <t>DEID ALEXANDER</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>29/09/2020</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,22 +3636,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>71718570</t>
+          <t>92321088</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CHUMPATI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GALA</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PATSI CINTHIA</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3660,21 +3660,21 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>05/02/2001</t>
+          <t>18/04/2021</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,22 +3699,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>46791163</t>
+          <t>44503468</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COTERA</t>
+          <t>CHUMPE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RODIL RENE</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,11 +3723,11 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16/12/1990</t>
+          <t>08/02/1983</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,22 +3762,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00092715</t>
+          <t>77503900</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CUEVA</t>
+          <t>COLACHAGUA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RICOPA</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ROSA MERY</t>
+          <t>SHEILA LETICIA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3786,11 +3786,11 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>07/06/1971</t>
+          <t>08/10/1995</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3825,35 +3825,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>92446495</t>
+          <t>92039400</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DAHUA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RUPAY</t>
+          <t>CAÑARI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DEYVI JACK</t>
+          <t>AZUMI SHANTAL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13/07/2021</t>
+          <t>29/09/2020</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,45 +3888,45 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>94396233</t>
+          <t>71718570</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DEXTRE</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>GALA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>GAEL KAYRO</t>
+          <t>PATSI CINTHIA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>05/02/2001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,40 +3951,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>92207811</t>
+          <t>75287007</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>ENERO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ERIK</t>
+          <t>KETTY DOMINICA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>30/09/1999</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,22 +4014,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>92222315</t>
+          <t>46791163</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>COTERA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ABDIEL JAZIEL</t>
+          <t>RODIL RENE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,21 +4038,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>16/12/1990</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,22 +4077,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>42413512</t>
+          <t>00092715</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>CUEVA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>RICOPA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JAZMIN BETZABETH</t>
+          <t>ROSA MERY</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4101,11 +4101,11 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11/05/1984</t>
+          <t>07/06/1971</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,27 +4140,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>92489713</t>
+          <t>92446495</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>DAHUA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RUPAY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>INGRID ASTRID</t>
+          <t>DEYVI JACK</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>13/07/2021</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,45 +4203,45 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>75318534</t>
+          <t>94396233</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>DEXTRE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ARISBEL ARIANA</t>
+          <t>GAEL KAYRO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>09/04/2006</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>76156896</t>
+          <t>92207811</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EUSTAQUIO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BENITES</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JAVIER</t>
+          <t>ERIK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>09/07/1999</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4329,27 +4329,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>92194218</t>
+          <t>92222315</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ESPINO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>ABDIEL JAZIEL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,45 +4392,45 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>92222175</t>
+          <t>42413512</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PORTOCARRERO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SAMIR MILER</t>
+          <t>JAZMIN BETZABETH</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>11/05/1984</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,45 +4455,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>42214488</t>
+          <t>92489713</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>GARCIA</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ROJAS</t>
-        </is>
-      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JAIME TEOFILO</t>
+          <t>INGRID ASTRID</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>12/08/1982</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>94642996</t>
+          <t>75318534</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GASTELU</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CABEZAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ABIGAIL MEDALI</t>
+          <t>ARISBEL ARIANA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,21 +4542,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>09/04/2006</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>94445786</t>
+          <t>81832382</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>EUSEBIO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>OLAYA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CLEIDER</t>
+          <t>HIMER JESHUA BRYANT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,11 +4605,11 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>24/09/2021</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,22 +4644,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>91885374</t>
+          <t>76156896</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GUEROVICH</t>
+          <t>EUSTAQUIO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ARANCEL</t>
+          <t>BENITES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ADRIEL JORGE</t>
+          <t>JAVIER</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,21 +4668,21 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>09/06/2020</t>
+          <t>09/07/1999</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,45 +4707,45 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>75101251</t>
+          <t>92194218</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GUILLEN</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ESPINO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ELMER</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14/01/2001</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,45 +4770,45 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20996386</t>
+          <t>92222175</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUAMANCHAHUA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PORTOCARRERO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FRICIA ELIZABETH</t>
+          <t>SAMIR MILER</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02/06/1971</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,45 +4833,45 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>94047252</t>
+          <t>42214488</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HUANICO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>JAIME TEOFILO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>12/08/1982</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>78765946</t>
+          <t>94642996</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HUAYTARA</t>
+          <t>GASTELU</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CABEZAS</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>YARISLEY DAFNE</t>
+          <t>ABIGAIL MEDALI</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>24/08/2014</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,45 +4959,45 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>70809810</t>
+          <t>94445786</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JAQUELINE MAYUMI</t>
+          <t>CLEIDER</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>15/08/2001</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,35 +5022,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>92445032</t>
+          <t>91885374</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>GUEROVICH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>ARANCEL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LINDA YEIS</t>
+          <t>ADRIEL JORGE</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>09/06/2020</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,22 +5085,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>42901772</t>
+          <t>75101251</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>GUILLEN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>ELMER</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5109,16 +5109,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>06/08/1982</t>
+          <t>14/01/2001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,22 +5148,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>92082689</t>
+          <t>76918087</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LANAZCA</t>
+          <t>GUIZADO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SIERRA</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>JORGE ALEJANDRO</t>
+          <t>RANDY</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>28/10/2020</t>
+          <t>05/02/1998</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,40 +5211,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>75001764</t>
+          <t>20996386</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>HUAMANCHAHUA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LUIGUI DANIEL</t>
+          <t>FRICIA ELIZABETH</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>13/04/2001</t>
+          <t>02/06/1971</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,45 +5274,45 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>76412062</t>
+          <t>94047252</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>HUANICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SERGIO RAFAEL</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14/11/2003</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,45 +5337,45 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>92193263</t>
+          <t>78765946</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LIMACHE</t>
+          <t>HUAYTARA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>IKER NOAH</t>
+          <t>YARISLEY DAFNE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>24/08/2014</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,40 +5400,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20580064</t>
+          <t>70809810</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LLANCACHAGUA</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HUACCHO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JORGE PAPA</t>
+          <t>JAQUELINE MAYUMI</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23/06/1944</t>
+          <t>15/08/2001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,22 +5463,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>92469548</t>
+          <t>92445032</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LOZADA</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CATALEYA ZEYNEP</t>
+          <t>LINDA YEIS</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>43511339</t>
+          <t>42901772</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ECHABAUDES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DAYSY</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>19/12/1985</t>
+          <t>06/08/1982</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,35 +5589,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>94615934</t>
+          <t>92082689</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MALVEÑO</t>
+          <t>LANAZCA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>SIERRA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MAYURI</t>
+          <t>JORGE ALEJANDRO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>28/10/2020</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>70606096</t>
+          <t>75001764</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PERCY JESUS</t>
+          <t>LUIGUI DANIEL</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,11 +5676,11 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>05/08/1998</t>
+          <t>13/04/2001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>94618669</t>
+          <t>76412062</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MATA</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EMIR RUBEN</t>
+          <t>SERGIO RAFAEL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>14/11/2003</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,22 +5778,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>92039861</t>
+          <t>92193263</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MATENCIOS</t>
+          <t>LIMACHE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>JHASTIN YANDEL</t>
+          <t>IKER NOAH</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,11 +5802,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>30/09/2020</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,45 +5841,45 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>94307754</t>
+          <t>20580064</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MAYBANTI</t>
+          <t>LLANCACHAGUA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ÑACO</t>
+          <t>HUACCHO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MEDALY ESTHER</t>
+          <t>JORGE PAPA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>23/06/1944</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,22 +5904,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>92194352</t>
+          <t>92469548</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>LOZADA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PILAR INGRID</t>
+          <t>CATALEYA ZEYNEP</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,40 +5967,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>77016635</t>
+          <t>43511339</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>ECHABAUDES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BERRY</t>
+          <t>DAYSY</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>19/11/2001</t>
+          <t>19/12/1985</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,45 +6030,45 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>76321000</t>
+          <t>94615934</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MELGAREJO</t>
+          <t>MALVEÑO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE</t>
+          <t>MAYURI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14/12/2001</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,22 +6093,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>47211525</t>
+          <t>70606096</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BELLIDO</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MARCIAL LINDO</t>
+          <t>PERCY JESUS</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>03/03/1991</t>
+          <t>05/08/1998</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,45 +6156,45 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>77042300</t>
+          <t>94618669</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MATA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>JENNIFER PILAR</t>
+          <t>EMIR RUBEN</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>01/08/2005</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,45 +6219,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>77418210</t>
+          <t>92039861</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MERINO</t>
+          <t>MATENCIOS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ENCISO</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>JUDITH</t>
+          <t>JHASTIN YANDEL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>28/02/1999</t>
+          <t>30/09/2020</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,22 +6282,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>92040429</t>
+          <t>94307754</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MAYBANTI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>ÑACO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>MEDALY ESTHER</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>30/09/2020</t>
+          <t>09/07/2025</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,45 +6345,45 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>41594775</t>
+          <t>92194352</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>HERNAN</t>
+          <t>PILAR INGRID</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>25/10/1982</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,45 +6408,45 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>92192495</t>
+          <t>77016635</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ALESSIA YATZIRI</t>
+          <t>BERRY</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>19/11/2001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,22 +6471,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>47760020</t>
+          <t>76321000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MUNGUI</t>
+          <t>MELGAREJO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ZACARIAS</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CLEVER</t>
+          <t>LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,16 +6495,16 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>19/10/1989</t>
+          <t>14/12/2001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,45 +6534,45 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>92911456</t>
+          <t>47211525</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MURAYARI</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LOZANO</t>
+          <t>BELLIDO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>YARITZA ITZEL</t>
+          <t>MARCIAL LINDO</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>29/05/2022</t>
+          <t>03/03/1991</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,22 +6597,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>76927877</t>
+          <t>74281497</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ATAPOMA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>JUAN DAVID</t>
+          <t>ELDER MESIAS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6621,16 +6621,16 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>06/04/2006</t>
+          <t>12/07/1995</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,45 +6660,45 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>94682414</t>
+          <t>77042300</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RONY CESAR</t>
+          <t>JENNIFER PILAR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>01/08/2005</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,45 +6723,45 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>94398586</t>
+          <t>77418210</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OCARI</t>
+          <t>MERINO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ZACARIAS</t>
+          <t>ENCISO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ZHENYI KENYI</t>
+          <t>JUDITH</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>28/09/2025</t>
+          <t>28/02/1999</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>91883930</t>
+          <t>92040429</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HUAYA</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ARIANA AMELY</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>30/09/2020</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,35 +6849,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>46449555</t>
+          <t>41594775</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BRAÑES</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NADIA TANIA</t>
+          <t>HERNAN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>28/04/1990</t>
+          <t>25/10/1982</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>41517689</t>
+          <t>92192495</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NILDA YANET</t>
+          <t>ALESSIA YATZIRI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>15/10/1982</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>92489139</t>
+          <t>47760020</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OSORES</t>
+          <t>MUNGUI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LLAMUCO</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>IAN KARPER</t>
+          <t>CLEVER</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>19/10/1989</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,35 +7038,35 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>92087755</t>
+          <t>92911456</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>MURAYARI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>LOZANO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ALFONSO BRANT</t>
+          <t>YARITZA ITZEL</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>31/10/2020</t>
+          <t>29/05/2022</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>91885525</t>
+          <t>76927877</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PACHIRI</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CAYETANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>JUAN BENJAMIN</t>
+          <t>JUAN DAVID</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,21 +7125,21 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>09/06/2020</t>
+          <t>06/04/2006</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,22 +7164,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>94191376</t>
+          <t>94682414</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PAIMA</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>QUENTISHA</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LIAM MAIKEL</t>
+          <t>RONY CESAR</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7188,11 +7188,11 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>92451937</t>
+          <t>94398586</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>OCARI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>HUARACC</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NEHEMIAS RICHARD</t>
+          <t>ZHENYI KENYI</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>28/09/2025</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,22 +7290,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>82244708</t>
+          <t>91883930</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PATRICIO</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SANTOMA</t>
+          <t>HUAYA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>ARIANA AMELY</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,22 +7353,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>49103748</t>
+          <t>46449555</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PICHUCA</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PIUNCA</t>
+          <t>BRAÑES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>HILARIA</t>
+          <t>NADIA TANIA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>30/03/1956</t>
+          <t>28/04/1990</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>92222558</t>
+          <t>41517689</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PIORI</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SHUNAXHI SUSEJ</t>
+          <t>NILDA YANET</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>15/10/1982</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,45 +7479,45 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>80581038</t>
+          <t>92489139</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PIZANGO</t>
+          <t>OSORES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>LLAMUCO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ARMILDA</t>
+          <t>IAN KARPER</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>23/11/1977</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,22 +7542,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>41898437</t>
+          <t>92087755</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PLAZA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MELVIN ANGEL</t>
+          <t>ALFONSO BRANT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7566,16 +7566,16 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>27/01/1983</t>
+          <t>31/10/2020</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>75313928</t>
+          <t>91885525</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>PACHIRI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>CAYETANO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DAMMARO LUCERO</t>
+          <t>JUAN BENJAMIN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>19/07/2005</t>
+          <t>09/06/2020</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>91689899</t>
+          <t>94191376</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PUENTE</t>
+          <t>PAIMA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>QUENTISHA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EDRICK LEODAD JHONNY</t>
+          <t>LIAM MAIKEL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,11 +7692,11 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,22 +7731,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>92464778</t>
+          <t>92451937</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CHIMANCA</t>
+          <t>HUARACC</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ELFREN HONLY</t>
+          <t>NEHEMIAS RICHARD</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>19/07/2021</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,22 +7794,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>92468805</t>
+          <t>82244708</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PATRICIO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GAMARRA</t>
+          <t>SANTOMA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LUZ ADRIANA</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>28/07/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,45 +7857,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>94498440</t>
+          <t>49103748</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PICHUCA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SHAMPIRI</t>
+          <t>PIUNCA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DAVID YAISON</t>
+          <t>HILARIA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>27/04/2025</t>
+          <t>30/03/1956</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,45 +7920,45 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>71748491</t>
+          <t>92222558</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PIORI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>JOSEPH RICHARD</t>
+          <t>SHUNAXHI SUSEJ</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>22/10/2000</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,45 +7983,45 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>92193866</t>
+          <t>80581038</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>PIZANGO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>GERARD THIAGO</t>
+          <t>ARMILDA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>23/11/1977</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>41991155</t>
+          <t>41898437</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>PLAZA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ALFREDO GRIMALDO</t>
+          <t>MELVIN ANGEL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,11 +8070,11 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>09/12/1981</t>
+          <t>27/01/1983</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8109,35 +8109,35 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>60409386</t>
+          <t>75313928</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>JHAFFET GERALDO</t>
+          <t>DAMMARO LUCERO</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>04/07/2006</t>
+          <t>19/07/2005</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,22 +8172,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>70469034</t>
+          <t>91689899</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PUENTE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SANDRO WUILY</t>
+          <t>EDRICK LEODAD JHONNY</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8196,21 +8196,21 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>19/02/2001</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,45 +8235,45 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>47902175</t>
+          <t>92464778</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>CHIMANCA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MARIA DE JESUS ELVIA</t>
+          <t>ELFREN HONLY</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>07/01/1988</t>
+          <t>19/07/2021</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,27 +8298,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>92236279</t>
+          <t>92468805</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ROSPIGLIOSI</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OLAYA</t>
+          <t>GAMARRA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NEYER MEYER</t>
+          <t>LUZ ADRIANA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>15/01/2021</t>
+          <t>28/07/2021</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,45 +8361,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>61256292</t>
+          <t>94498440</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>SHAMPIRI</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AZUMI YUYIN KAROL</t>
+          <t>DAVID YAISON</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>23/05/2007</t>
+          <t>27/04/2025</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,40 +8424,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>91996488</t>
+          <t>71748491</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SACCSA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ASHLY TERESA</t>
+          <t>JOSEPH RICHARD</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>01/09/2020</t>
+          <t>22/10/2000</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,45 +8487,45 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>70737398</t>
+          <t>92193866</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NEMERLY KEYLA</t>
+          <t>GERARD THIAGO</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>08/05/2007</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>44404892</t>
+          <t>41991155</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LUIS MANUEL</t>
+          <t>ALFREDO GRIMALDO</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,11 +8574,11 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>30/06/1985</t>
+          <t>09/12/1981</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8613,40 +8613,40 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>73962347</t>
+          <t>60409386</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SALHUANA</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>CAMILA ALEJANDRA</t>
+          <t>JHAFFET GERALDO</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>08/12/1996</t>
+          <t>04/07/2006</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21001701</t>
+          <t>70469034</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>SANDRO WUILY</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>21/04/1972</t>
+          <t>19/02/2001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,35 +8739,35 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>48423925</t>
+          <t>47902175</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ALANYA</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>RICHARD RONALD</t>
+          <t>MARIA DE JESUS ELVIA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>08/01/1993</t>
+          <t>07/01/1988</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,22 +8802,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>94521679</t>
+          <t>92236279</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROSPIGLIOSI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>OLAYA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>NEYER MEYER</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8826,11 +8826,11 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>18/01/2026</t>
+          <t>15/01/2021</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,45 +8865,45 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>76320981</t>
+          <t>94421184</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DEYSI LUZCLARITA</t>
+          <t>ALFONSO BENJAMIN</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>26/12/2001</t>
+          <t>19/10/2025</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,45 +8928,45 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>91994097</t>
+          <t>61256292</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SANTISTEBAN</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CAMILO GABRIEL</t>
+          <t>AZUMI YUYIN KAROL</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>29/08/2020</t>
+          <t>23/05/2007</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,35 +8991,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>92655755</t>
+          <t>91996488</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>SACCSA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CHUMPATE</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GAEL GABRIEL</t>
+          <t>ASHLY TERESA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>27/07/2021</t>
+          <t>01/09/2020</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>76401299</t>
+          <t>70737398</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CARNICA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AQUILA CIELO</t>
+          <t>NEMERLY KEYLA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,11 +9078,11 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>05/04/2002</t>
+          <t>08/05/2007</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,45 +9117,45 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>92216101</t>
+          <t>44404892</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ANTONELA</t>
+          <t>LUIS MANUEL</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>30/06/1985</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,22 +9180,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>92450307</t>
+          <t>73962347</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SEGUNDO</t>
+          <t>SALHUANA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MISHICURI</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ANALY YANIRA</t>
+          <t>CAMILA ALEJANDRA</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9204,21 +9204,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>08/12/1996</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,45 +9243,45 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>92471551</t>
+          <t>21001701</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SHAMUYA</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MAILY KASUMI</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>21/04/1972</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9306,22 +9306,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>44606371</t>
+          <t>48423925</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SINCHE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>ALANYA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>JOSE ANGEL</t>
+          <t>RICHARD RONALD</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9330,11 +9330,11 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>13/09/1986</t>
+          <t>08/01/1993</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9369,45 +9369,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>73441118</t>
+          <t>94521679</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SORIANO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NATALI VANESSA</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>08/10/1996</t>
+          <t>18/01/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9432,40 +9432,40 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>48477472</t>
+          <t>76320981</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BARJA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LUIS MIGUEL</t>
+          <t>DEYSI LUZCLARITA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>08/12/1993</t>
+          <t>26/12/2001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9495,27 +9495,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>91993771</t>
+          <t>91994097</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CARHUAMACA</t>
+          <t>SANTISTEBAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>BLANCA ABIGAIL</t>
+          <t>CAMILO GABRIEL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -9558,27 +9558,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>92445123</t>
+          <t>92655755</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SUMAYLLO</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CANCHANYA</t>
+          <t>CHUMPATE</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DAYANA SAMANTHA</t>
+          <t>GAEL GABRIEL</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>27/07/2021</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9621,35 +9621,35 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>62391082</t>
+          <t>76401299</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TABRA</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CARNICA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>JOSUE BEQUER</t>
+          <t>AQUILA CIELO</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>22/07/2007</t>
+          <t>05/04/2002</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9684,22 +9684,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>91688446</t>
+          <t>92216101</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TAYPE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>BRISEIDA REYNA</t>
+          <t>ANTONELA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>19/01/2020</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>19/01/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9747,35 +9747,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>91812793</t>
+          <t>92450307</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TENAZOA</t>
+          <t>SEGUNDO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NINA</t>
+          <t>MISHICURI</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ABNER ANTOÑIO</t>
+          <t>ANALY YANIRA</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>13/04/2020</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,22 +9810,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>61056507</t>
+          <t>92471551</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SHAMUYA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MAYLITH MELIZA</t>
+          <t>MAILY KASUMI</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9834,21 +9834,21 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>26/03/2001</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,22 +9873,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>94562648</t>
+          <t>44606371</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SINCHE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>IAN DARKIEL</t>
+          <t>JOSE ANGEL</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>13/09/1986</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,22 +9936,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>92078620</t>
+          <t>73441118</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TUPIÑO</t>
+          <t>SORIANO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ALIZEE MIA LIA</t>
+          <t>NATALI VANESSA</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9960,16 +9960,16 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>25/10/2020</t>
+          <t>08/10/1996</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,22 +9999,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>44002317</t>
+          <t>48477472</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UMPIQUIRI</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MAXIMO</t>
+          <t>BARJA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO</t>
+          <t>LUIS MIGUEL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10023,11 +10023,11 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>06/01/1987</t>
+          <t>08/12/1993</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,22 +10062,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>44869785</t>
+          <t>91993771</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>CARHUAMACA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>MARGARITA ELIZABETH</t>
+          <t>BLANCA ABIGAIL</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10086,21 +10086,21 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>05/02/1988</t>
+          <t>29/08/2020</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,22 +10125,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>92319511</t>
+          <t>94654565</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>DOMINGUILLO</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AXEL RAYAN</t>
+          <t>LEANDER</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10149,11 +10149,11 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>17/04/2021</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,27 +10188,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>92319692</t>
+          <t>92445123</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>SUMAYLLO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>CANCHANYA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ALVARO MARIANO</t>
+          <t>DAYANA SAMANTHA</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>17/04/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,22 +10251,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>91689659</t>
+          <t>62391082</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TABRA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>JAYO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>GIANNI SEBASTIAN</t>
+          <t>JOSUE BEQUER</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10275,21 +10275,21 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>22/07/2007</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,45 +10314,45 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>48389861</t>
+          <t>91688446</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>TAYPE</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>BILL CLINTON</t>
+          <t>BRISEIDA REYNA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>22/01/1993</t>
+          <t>19/01/2020</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>19/01/2025</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,22 +10377,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>76669305</t>
+          <t>91812793</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>TENAZOA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>NINA</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>ABNER ANTOÑIO</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10401,16 +10401,16 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>07/04/2000</t>
+          <t>13/04/2020</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,22 +10440,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>91897894</t>
+          <t>61056507</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>VILLANTOY</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PAUCARCAJA</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PRIYA MARBY</t>
+          <t>MAYLITH MELIZA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>19/06/2020</t>
+          <t>26/03/2001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,35 +10503,35 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>92451044</t>
+          <t>94562648</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>VILLAS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ROFINO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ARIELA ARELIS</t>
+          <t>IAN DARKIEL</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,45 +10566,45 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>91688260</t>
+          <t>44002317</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ZEGARRA</t>
+          <t>UMPIQUIRI</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>LACMA</t>
+          <t>MAXIMO</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LUZ ESTRELLA</t>
+          <t>MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>19/01/2020</t>
+          <t>06/01/1987</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>19/01/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,63 +10629,945 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>44869785</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>UNCHUPAICO</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MAYTA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>MARGARITA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>38</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>05/02/1988</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>11/02/2025</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>92492618</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>URCUCULLAY</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AMES</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>YAMELEY KEIRA</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>5</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>14/08/2021</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>71667483</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>URPI</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>RAQUEL YENIFER</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>23</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>15/07/2003</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>92319511</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>AXEL RAYAN</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>5</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>17/04/2021</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>92535587</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>VARA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>URBINA</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>GIAN ELIUD</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>5</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>13/09/2021</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>92319692</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>HUAMAN</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ALVARO MARIANO</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>5</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>17/04/2021</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>91689659</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>JAYO</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>GIANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>6</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20/01/2020</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>20/01/2025</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>60669526</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PEÑA</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>JOSE MAURICIO</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>18</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>10/09/2008</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M170" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>48389861</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ALIAGA</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BILL CLINTON</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>33</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>22/01/1993</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M171" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>76669305</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>JHON</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>26</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>07/04/2000</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M172" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>91897894</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>VILLANTOY</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>PAUCARCAJA</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PRIYA MARBY</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>6</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>19/06/2020</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>19/06/2025</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M173" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>92451044</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>VILLAS</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ROFINO</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ARIELA ARELIS</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>5</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>16/07/2021</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M174" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>91688260</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ZEGARRA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LACMA</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>LUZ ESTRELLA</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>6</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>19/01/2020</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>19/01/2025</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M175" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>92040235</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>ZUMAETA</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>VELASQUEZ</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>DAYL KIM</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F163" t="n">
+      <c r="F176" t="n">
         <v>6</v>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>30/09/2020</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H176" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I176" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>MAZAMARI</t>
-        </is>
-      </c>
-      <c r="M163" t="n">
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M176" t="n">
+        <v>120604</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>94762442</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ÑACO</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SACARIAS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>MERY LARICO</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>MAZAMARI</t>
+        </is>
+      </c>
+      <c r="M177" t="n">
         <v>120604</v>
       </c>
     </row>
